--- a/out/MLP-mamba2_repeat_2_000001.xlsx
+++ b/out/MLP-mamba2_repeat_2_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.818340913531692</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.418340913531692</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.418340913531692</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.418340913531692</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.418340913531692</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.418340913531692</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6252523530368312</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.418340913531692</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.418340913531692</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.818340913531692</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.225252353036831</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.418340913531692</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.418340913531692</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.418340913531692</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.418340913531692</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.418340913531692</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.418340913531692</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002975189137740527</v>
+        <v>-0.0002852461982754757</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1281030061330229</v>
+        <v>0.1228186240889292</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.418340913531692</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2565478853200842</v>
+        <v>0.2459652335842342</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4949288330071062</v>
+        <v>0.474514125262715</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.418340913531692</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.11863179375673</v>
+        <v>1.072488725084198</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1522433924731555</v>
+        <v>0.1459632049202166</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.9275615507088569</v>
+        <v>0.8893003148215329</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.0308913168179165</v>
+        <v>0.02961681348275625</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.8368626216130755</v>
+        <v>0.8023428051754744</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02675325326362355</v>
+        <v>0.02564983452094541</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.8594436605561309</v>
+        <v>0.8239925053630751</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01307870851712196</v>
+        <v>0.01253927213630021</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.818340913531692</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.8588140156052569</v>
+        <v>0.8233888297036842</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.006240400049019</v>
+        <v>0.00598248580713162</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8581998802210272</v>
+        <v>0.8227998176996869</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002596506778809053</v>
+        <v>0.002489618419825244</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.418340913531692</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.8571458808117384</v>
+        <v>0.821789025640114</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001798396272191047</v>
+        <v>0.001723544137658513</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.8581432538304526</v>
+        <v>0.8227450091788431</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0007475272436399872</v>
+        <v>0.0007166014665040973</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.418340913531692</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.8578385966052458</v>
+        <v>0.8224526613928564</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003852122208866049</v>
+        <v>0.0003691761022200321</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.225252353036831</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.8578607334445298</v>
+        <v>0.8224736840023049</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001482603132434679</v>
+        <v>0.0001419619442060651</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.8577714392006477</v>
+        <v>0.8223878480090054</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>7.860445615503979e-05</v>
+        <v>7.516865658702444e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.8577802646958914</v>
+        <v>0.8223961072986871</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.622103644974442e-05</v>
+        <v>3.452702125317959e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.8577739997988642</v>
+        <v>0.8223898940561505</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.471454777712014e-05</v>
+        <v>1.364889654592446e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.8577665945595121</v>
+        <v>0.8223825869453585</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.8577589194557981</v>
+        <v>0.8223749835814947</v>
       </c>
     </row>
     <row r="60">
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8577530009029273</v>
+        <v>0.8223691128551907</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.410678356938051e-06</v>
+        <v>-3.728542685550439e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.225252353036831</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.8577470394743427</v>
+        <v>0.8223632480591894</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.225252353036831</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.8577413602976345</v>
+        <v>0.8223575688824812</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.418340913531692</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.8577364789993851</v>
+        <v>0.8223526875842319</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.8577315577978373</v>
+        <v>0.822347766382684</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.418340913531692</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.8577315498267428</v>
+        <v>0.8223477584115896</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6252523530368312</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.857731709248632</v>
+        <v>0.8223479178334786</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.418340913531692</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.8577316135954985</v>
+        <v>0.8223478221803452</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.8577319643236547</v>
+        <v>0.8223481729085015</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.8577317172197264</v>
+        <v>0.8223479258045732</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.8577316773642542</v>
+        <v>0.8223478859491008</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.8577316135954985</v>
+        <v>0.8223478221803452</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.8577316853353486</v>
+        <v>0.8223478939201952</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.8577316135954985</v>
+        <v>0.8223478221803452</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>2.418340913531692</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.8577317172197264</v>
+        <v>0.8223479258045732</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.8577318128728602</v>
+        <v>0.8223480214577068</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.8577317491041042</v>
+        <v>0.822347957688951</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.857731709248632</v>
+        <v>0.8223479178334786</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.225252353036831</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.8577316853353486</v>
+        <v>0.8223478939201952</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.8577314382314205</v>
+        <v>0.8223476468162672</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.8577313585204757</v>
+        <v>0.8223475671053224</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>2.418340913531692</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.8577314063470424</v>
+        <v>0.8223476149318891</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.8577315259134595</v>
+        <v>0.8223477344983062</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.8577315099712706</v>
+        <v>0.8223477185561172</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.8577315259134595</v>
+        <v>0.8223477344983062</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.418340913531692</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.8577315099712706</v>
+        <v>0.8223477185561172</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.8577315657689317</v>
+        <v>0.8223477743537785</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.8577315657689317</v>
+        <v>0.8223477743537785</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.818340913531692</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.8577315657689317</v>
+        <v>0.8223477743537785</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.8577317172197264</v>
+        <v>0.8223479258045732</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.418340913531692</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.8577319324392769</v>
+        <v>0.8223481410241237</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.857731844757238</v>
+        <v>0.8223480533420846</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.8577317969306713</v>
+        <v>0.8223480055155179</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.857731844757238</v>
+        <v>0.8223480533420846</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.8577316614220653</v>
+        <v>0.8223478700069119</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.8577316693931597</v>
+        <v>0.8223478779780063</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.818340913531692</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.8577316773642542</v>
+        <v>0.8223478859491008</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.8577316853353486</v>
+        <v>0.8223478939201952</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.8577316853353486</v>
+        <v>0.8223478939201952</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.818340913531692</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.8577317251908209</v>
+        <v>0.8223479337756676</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.418340913531692</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.8577317889595768</v>
+        <v>0.8223479975444234</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6252523530368312</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.8577319005548991</v>
+        <v>0.8223481091397459</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.8577319483814658</v>
+        <v>0.8223481569663126</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.8577319085259936</v>
+        <v>0.8223481171108403</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.818340913531692</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.8577318367861435</v>
+        <v>0.8223480453709902</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.8577319563525603</v>
+        <v>0.822348164937407</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6252523530368312</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.8577317969306713</v>
+        <v>0.8223480055155179</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.8577315657689317</v>
+        <v>0.8223477743537785</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.857731517942365</v>
+        <v>0.8223477265272118</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.8577315498267428</v>
+        <v>0.8223477584115896</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8577316135954985</v>
+        <v>0.8223478221803452</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8577316135954985</v>
+        <v>0.8223478221803452</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.8577315338845539</v>
+        <v>0.8223477424694007</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.8577314143181368</v>
+        <v>0.8223476229029836</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.418340913531692</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.8577313744626646</v>
+        <v>0.8223475830475113</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.418340913531692</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.857731517942365</v>
+        <v>0.8223477265272118</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.8577316534509708</v>
+        <v>0.8223478620358174</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.8577316375087819</v>
+        <v>0.8223478460936285</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.8577316135954985</v>
+        <v>0.8223478221803452</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.8577315737400262</v>
+        <v>0.8223477823248729</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.225252353036831</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.8577314701157983</v>
+        <v>0.822347678700645</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.418340913531692</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.8577313505493812</v>
+        <v>0.822347559134228</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.8577314701157983</v>
+        <v>0.822347678700645</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.418340913531692</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.857731517942365</v>
+        <v>0.8223477265272118</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.8577316135954985</v>
+        <v>0.8223478221803452</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.8577314940290817</v>
+        <v>0.8223477026139283</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.8577315020001761</v>
+        <v>0.8223477105850228</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_2_000001.xlsx
+++ b/out/MLP-mamba2_repeat_2_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.3690589350268096</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.818340913531692</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.418340913531692</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.474458756368113</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.818340913531692</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002975189137740527</v>
+        <v>-0.0002317079037269577</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1281030061330229</v>
+        <v>0.09976658888247654</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2565478853200842</v>
+        <v>0.1997996433841223</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4949288330071062</v>
+        <v>0.3854519221161948</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.11863179375673</v>
+        <v>0.871191813841566</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1522433924731555</v>
+        <v>0.1185671719753087</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.9275615507088569</v>
+        <v>0.7223862860692138</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.0308913168179165</v>
+        <v>0.02405816117332962</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.8368626216130755</v>
+        <v>0.6517499494152468</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02675325326362355</v>
+        <v>0.02083543679024599</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.8594436605561309</v>
+        <v>0.6693360652016147</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01307870851712196</v>
+        <v>0.01018562235019855</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.818340913531692</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.8588140156052569</v>
+        <v>0.6688456978386569</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.006240400049019</v>
+        <v>0.00485862115724931</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.7168981654917838</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8581998802210272</v>
+        <v>0.6683663002260444</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002596506778809053</v>
+        <v>0.002021425139068041</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.418340913531692</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.8571458808117384</v>
+        <v>0.6675442765489977</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001798396272191047</v>
+        <v>0.001399442111847542</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.8581432538304526</v>
+        <v>0.6683199008083304</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0007475272436399872</v>
+        <v>0.0005813011915345791</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.418340913531692</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.8578385966052458</v>
+        <v>0.6680815343564441</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003852122208866049</v>
+        <v>0.0002990180830537761</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.8578607334445298</v>
+        <v>0.6680976582970782</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001482603132434679</v>
+        <v>0.0001141441476242028</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.8577714392006477</v>
+        <v>0.668027096243853</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>7.860445615503979e-05</v>
+        <v>6.028019179229133e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.8577802646958914</v>
+        <v>0.6680328541495323</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.622103644974442e-05</v>
+        <v>2.718628873473194e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.8577739997988642</v>
+        <v>0.6680268727142149</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.471454777712014e-05</v>
+        <v>9.919117236739567e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.8577665945595121</v>
+        <v>0.6680200206487056</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.301093358848441e-06</v>
+        <v>1.456405945771008e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.8577589194557981</v>
+        <v>0.6680129240702947</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.279375894546688e-06</v>
+        <v>-2.106181251314092e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8577530009029273</v>
+        <v>0.6680071990121582</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.410678356938051e-06</v>
+        <v>-3.728542685550439e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.8577470394743427</v>
+        <v>0.6680014298692907</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.8577413602976345</v>
+        <v>0.6679958862011882</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.418340913531692</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.8577364789993851</v>
+        <v>0.6679909650474668</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.8577315577978373</v>
+        <v>0.6679910049029391</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.418340913531692</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.8577315498267428</v>
+        <v>0.6679909969318446</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.857731709248632</v>
+        <v>0.6679911563537337</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.418340913531692</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.8577316135954985</v>
+        <v>0.6679910607006002</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.8577319643236547</v>
+        <v>0.6679914114287565</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.8577317172197264</v>
+        <v>0.6679911643248282</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.8577316773642542</v>
+        <v>0.6679911244693559</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.8577316135954985</v>
+        <v>0.6679910607006002</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.8577316853353486</v>
+        <v>0.6679911324404504</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.8577316135954985</v>
+        <v>0.6679910607006002</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>2.418340913531692</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.8577317172197264</v>
+        <v>0.6679911643248282</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.8577318128728602</v>
+        <v>0.6679912599779619</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.474458756368113</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.8577317491041042</v>
+        <v>0.667991196209206</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.857731709248632</v>
+        <v>0.6679911563537337</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.8577316853353486</v>
+        <v>0.6679911324404504</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.8577314382314205</v>
+        <v>0.6679908853365223</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.8577313585204757</v>
+        <v>0.6679908056255774</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.8577314063470424</v>
+        <v>0.6679908534521442</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.8577315259134595</v>
+        <v>0.6679909730185613</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.474458756368113</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.8577315099712706</v>
+        <v>0.6679909570763723</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.8577315259134595</v>
+        <v>0.6679909730185613</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.418340913531692</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.8577315099712706</v>
+        <v>0.6679909570763723</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.8577315657689317</v>
+        <v>0.6679910128740335</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.8577315657689317</v>
+        <v>0.6679910128740335</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.818340913531692</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.8577315657689317</v>
+        <v>0.6679910128740335</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.8577317172197264</v>
+        <v>0.6679911643248282</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.418340913531692</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.8577319324392769</v>
+        <v>0.6679913795443787</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.857731844757238</v>
+        <v>0.6679912918623397</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.418340913531692</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.8577317969306713</v>
+        <v>0.6679912440357729</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.857731844757238</v>
+        <v>0.6679912918623397</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.8577316614220653</v>
+        <v>0.667991108527167</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.8577316693931597</v>
+        <v>0.6679911164982615</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.818340913531692</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.8577316773642542</v>
+        <v>0.6679911244693559</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.8577316853353486</v>
+        <v>0.6679911324404504</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.8577316853353486</v>
+        <v>0.6679911324404504</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.818340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.8577317251908209</v>
+        <v>0.6679911722959226</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.8577317889595768</v>
+        <v>0.6679912360646785</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.8577319005548991</v>
+        <v>0.6679913476600009</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.8577319483814658</v>
+        <v>0.6679913954865676</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.8577319085259936</v>
+        <v>0.6679913556310954</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.818340913531692</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.8577318367861435</v>
+        <v>0.6679912838912453</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.8577319563525603</v>
+        <v>0.6679914034576621</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.8577317969306713</v>
+        <v>0.6679912440357729</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.8577315657689317</v>
+        <v>0.6679910128740335</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.857731517942365</v>
+        <v>0.6679909650474668</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.8577315498267428</v>
+        <v>0.6679909969318446</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8577316135954985</v>
+        <v>0.6679910607006002</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8577316135954985</v>
+        <v>0.6679910607006002</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.8577315338845539</v>
+        <v>0.6679909809896557</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.8577314143181368</v>
+        <v>0.6679908614232386</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.8577313744626646</v>
+        <v>0.6679908215677663</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.857731517942365</v>
+        <v>0.6679909650474668</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.8577316534509708</v>
+        <v>0.6679911005560726</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.474458756368113</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.8577316375087819</v>
+        <v>0.6679910846138837</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.8577316135954985</v>
+        <v>0.6679910607006002</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.8577315737400262</v>
+        <v>0.667991020845128</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.8577314701157983</v>
+        <v>0.6679909172209001</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.418340913531692</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.8577313505493812</v>
+        <v>0.667990797654483</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.8577314701157983</v>
+        <v>0.6679909172209001</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.418340913531692</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.857731517942365</v>
+        <v>0.6679909650474668</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.8577316135954985</v>
+        <v>0.6679910607006002</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.8577314940290817</v>
+        <v>0.6679909411341834</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.8577315020001761</v>
+        <v>0.6679909491052779</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_2_000001.xlsx
+++ b/out/MLP-mamba2_repeat_2_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.254026859998703</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.3690589350268096</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.8126565217971802</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.58</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.3511208593845367</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.2212197045618354</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.1586514860391617</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.2555831968784332</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.2384660989046097</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.2944251894950867</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.3249688744544983</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.5688538551330566</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.2500147223472595</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.2212197045618354</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.2281804531812668</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.474458756368113</v>
+        <v>0.16</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.2671531140804291</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.16</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.6016827821731567</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.6487135887145996</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.612576626421732</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.7627083659172058</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.612576626421732</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.5474710464477539</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.452356219291687</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.5182198882102966</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.6127690076828003</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.9168981654917838</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.3618902564048767</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.2466219216585159</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.2341649532318115</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.1502311825752258</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.548542857170105</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.3676774203777313</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.3334226906299591</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.3169575333595276</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.3906709253787994</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4915564954280853</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.16</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.1684287041425705</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4220077991485596</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.09873832017183304</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.16</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4844427704811096</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.2913370728492737</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.3873269259929657</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.395795464515686</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.5504410266876221</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.731162428855896</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.612576626421732</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.9199585318565369</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.612576626421732</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.7467487454414368</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.612576626421732</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.9679145812988281</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.612576626421732</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.7793278098106384</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.612576626421732</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002317079037269577</v>
+        <v>-0.0001702408744366839</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.09976658888247654</v>
+        <v>0.07330077777373428</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.8761178851127625</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.612576626421732</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1997996433841223</v>
+        <v>0.1467971759432526</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3854519221161948</v>
+        <v>0.2831996698953014</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.578470766544342</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.9168981654917838</v>
+        <v>-0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.871191813841566</v>
+        <v>0.6400831868157596</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1185671719753087</v>
+        <v>0.08711329698371349</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.02129091322422028</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.7223862860692138</v>
+        <v>0.5307526231656382</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02405816117332962</v>
+        <v>0.01767614252776867</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>0.3173766136169434</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.6517499494152468</v>
+        <v>0.4788543111816319</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02083543679024599</v>
+        <v>0.01530832500785563</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.04109012708067894</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.6693360652016147</v>
+        <v>0.4917752774562403</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01018562235019855</v>
+        <v>0.00748238961545394</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.5668535828590393</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.6688456978386569</v>
+        <v>0.4914138391048955</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.00485862115724931</v>
+        <v>0.003568381776201306</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.3043122589588165</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.7168981654917838</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.6683663002260444</v>
+        <v>0.4910602829844139</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002021425139068041</v>
+        <v>0.001483643082930753</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.6221125721931458</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.6675442765489977</v>
+        <v>0.4904549732263382</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001399442111847542</v>
+        <v>0.001026724782164925</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.2042546570301056</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.9168981654917838</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.6683199008083304</v>
+        <v>0.4910236470363983</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005813011915345791</v>
+        <v>0.0004260280188314653</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.716177761554718</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.02121970456183539</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.6680815343564441</v>
+        <v>0.4908470842272644</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002990180830537761</v>
+        <v>0.0002181693181098049</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.3177483081817627</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.2212197045618354</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.6680976582970782</v>
+        <v>0.4908576145057606</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001141441476242028</v>
+        <v>8.265230243718883e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.2111958563327789</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.668027096243853</v>
+        <v>0.4908043437054495</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>6.028019179229133e-05</v>
+        <v>4.310119395221467e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.3136945366859436</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.6680328541495323</v>
+        <v>0.4908072705833183</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.718628873473194e-05</v>
+        <v>1.871621275190775e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.2120146006345749</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.6680268727142149</v>
+        <v>0.4908015474204531</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>9.919117236739567e-06</v>
+        <v>6.189337927554673e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.2785477936267853</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.6680200206487056</v>
+        <v>0.4907951822846045</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.456405945771008e-06</v>
+        <v>-3.882814673064221e-07</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>0.238555833697319</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6680129240702947</v>
+        <v>0.4907886642314969</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.106181251314092e-06</v>
+        <v>-2.932986608081494e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.2418629974126816</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6680071990121582</v>
+        <v>0.4907831326680945</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.728542685550439e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.1265262067317963</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.16</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.6680014298692907</v>
+        <v>0.4907775558109437</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.4469153881072998</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.6679958862011882</v>
+        <v>0.4907721484682867</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.5205200910568237</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.6679909650474668</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.3396894633769989</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6679910049029391</v>
+        <v>0.4907672671700376</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.7532278299331665</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.6679909969318446</v>
+        <v>0.4907672591989432</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.201208159327507</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.16</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6679911563537337</v>
+        <v>0.4907674186208323</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.9251775741577148</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6679910607006002</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.1839857697486877</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.2212197045618354</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6679914114287565</v>
+        <v>0.4907676736958551</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.1416998356580734</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6679911643248282</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.368494838476181</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6679911244693559</v>
+        <v>0.4907673867364544</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.4972214996814728</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.6679910607006002</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.2603820860385895</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6679911324404504</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.2430460453033447</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6679910607006002</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.9482558369636536</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6679911643248282</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.3305058479309082</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.2212197045618354</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6679912599779619</v>
+        <v>0.4907675222450604</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.1370992213487625</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.474458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.667991196209206</v>
+        <v>0.4907674584763045</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.2621249854564667</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6679911563537337</v>
+        <v>0.4907674186208323</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.09278812259435654</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6679911324404504</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.2026525139808655</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6679908853365223</v>
+        <v>0.4907671476036208</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.5252628326416016</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6679908056255774</v>
+        <v>0.490767067892676</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.6157029867172241</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6679908534521442</v>
+        <v>0.4907671157192427</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.2739202380180359</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6679909730185613</v>
+        <v>0.4907672352856598</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.473645031452179</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.474458756368113</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6679909570763723</v>
+        <v>0.4907672193434709</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.3819985091686249</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.02121970456183539</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6679909730185613</v>
+        <v>0.4907672352856598</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.5779328942298889</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.02121970456183539</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6679909570763723</v>
+        <v>0.4907672193434709</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3484295606613159</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6679910128740335</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3217560350894928</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6679910128740335</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.8410243988037109</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6679910128740335</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.3975610136985779</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.9168981654917838</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6679911643248282</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.699972927570343</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.2212197045618354</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6679913795443787</v>
+        <v>0.4907676418114773</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.2506641149520874</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.9168981654917838</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6679912918623397</v>
+        <v>0.4907675541294382</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.5464195013046265</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.2212197045618354</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6679912440357729</v>
+        <v>0.4907675063028715</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.07968466728925705</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.2212197045618354</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6679912918623397</v>
+        <v>0.4907675541294382</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.3909324705600739</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.667991108527167</v>
+        <v>0.4907673707942655</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.3113847374916077</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6679911164982615</v>
+        <v>0.49076737876536</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.6276090145111084</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6679911244693559</v>
+        <v>0.4907673867364544</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.2790385484695435</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6679911324404504</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.4318370819091797</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.02121970456183539</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6679911324404504</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.7044160962104797</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6679911722959226</v>
+        <v>0.4907674345630212</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.5859952569007874</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6679912360646785</v>
+        <v>0.4907674983317771</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.4618848264217377</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6679913476600009</v>
+        <v>0.4907676099270994</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.2383410036563873</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.16</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6679913954865676</v>
+        <v>0.4907676577536662</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.2542849481105804</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6679913556310954</v>
+        <v>0.4907676178981939</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.6019470691680908</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6679912838912453</v>
+        <v>0.4907675461583438</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.105463020503521</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6679914034576621</v>
+        <v>0.4907676657247606</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.1325935870409012</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6679912440357729</v>
+        <v>0.4907675063028715</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.2480303943157196</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6679910128740335</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.4095050692558289</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6679909650474668</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.4863494038581848</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6679909969318446</v>
+        <v>0.4907672591989432</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3828014433383942</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6679910607006002</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.192096084356308</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.6679910607006002</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.2166753262281418</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6679909809896557</v>
+        <v>0.4907672432567542</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.2140226662158966</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6679908614232386</v>
+        <v>0.4907671236903371</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.7297660708427429</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6679908215677663</v>
+        <v>0.4907670838348649</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.619560182094574</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.6679909650474668</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4997704029083252</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6679911005560726</v>
+        <v>0.4907673628231711</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.1826610416173935</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.474458756368113</v>
+        <v>0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6679910846138837</v>
+        <v>0.4907673468809822</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.302655816078186</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6679910607006002</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.2234208583831787</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.667991020845128</v>
+        <v>0.4907672831122265</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.09578701108694077</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6679909172209001</v>
+        <v>0.4907671794879986</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.7995526194572449</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.667990797654483</v>
+        <v>0.4907670599215815</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3784999549388885</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6679909172209001</v>
+        <v>0.4907671794879986</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.6247038245201111</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6679909650474668</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.1967712342739105</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.6679910607006002</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3926559686660767</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.2299999999999999</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6679909411341834</v>
+        <v>0.4907672034012819</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4424172639846802</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.1599999999999999</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6679909491052779</v>
+        <v>0.4907672113723764</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_2_000001.xlsx
+++ b/out/MLP-mamba2_repeat_2_000001.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.254026859998703</v>
+        <v>0.2540268301963806</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.4399999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.2555831968784332</v>
+        <v>0.255583256483078</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.3249688744544983</v>
+        <v>0.3249688446521759</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.7199999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.2500147223472595</v>
+        <v>0.2500147521495819</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.1199999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.2281804531812668</v>
+        <v>0.2281804233789444</v>
       </c>
       <c r="JB12" t="n">
         <v>0.16</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.2671531140804291</v>
+        <v>0.2671532034873962</v>
       </c>
       <c r="JB13" t="n">
         <v>0.16</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.6487135887145996</v>
+        <v>0.6487135291099548</v>
       </c>
       <c r="JB15" t="n">
         <v>0.7199999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.5474710464477539</v>
+        <v>0.5474711656570435</v>
       </c>
       <c r="JB17" t="n">
         <v>0.8599999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.3618902564048767</v>
+        <v>0.3618902862071991</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.7199999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.2466219216585159</v>
+        <v>0.2466219812631607</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.8599999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.2341649532318115</v>
+        <v>0.2341649234294891</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.8599999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.1502311825752258</v>
+        <v>0.150231197476387</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.8599999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.3169575333595276</v>
+        <v>0.3169575035572052</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.7199999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.1684287041425705</v>
+        <v>0.1684287190437317</v>
       </c>
       <c r="JB31" t="n">
         <v>0.16</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.4220077991485596</v>
+        <v>0.4220078587532043</v>
       </c>
       <c r="JB32" t="n">
         <v>0.3</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.09873832017183304</v>
+        <v>0.09873829782009125</v>
       </c>
       <c r="JB33" t="n">
         <v>0.16</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.3873269259929657</v>
+        <v>0.3873268961906433</v>
       </c>
       <c r="JB36" t="n">
         <v>0.4399999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.5504410266876221</v>
+        <v>0.5504409670829773</v>
       </c>
       <c r="JB38" t="n">
         <v>0.7199999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.7793278098106384</v>
+        <v>0.7793277502059937</v>
       </c>
       <c r="JB43" t="n">
         <v>0.8599999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.578470766544342</v>
+        <v>0.5784708261489868</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.3</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.3173766136169434</v>
+        <v>0.3173765540122986</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.7199999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.04109012708067894</v>
+        <v>0.04109010845422745</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.8599999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.5668535828590393</v>
+        <v>0.5668535232543945</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.5799999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.3043122589588165</v>
+        <v>0.3043122291564941</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.5799999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.2042546570301056</v>
+        <v>0.2042547017335892</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.4399999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.716177761554718</v>
+        <v>0.7161778211593628</v>
       </c>
       <c r="JB53" t="n">
         <v>0.1600000000000001</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.3177483081817627</v>
+        <v>0.3177483677864075</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.1199999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.2111958563327789</v>
+        <v>0.2111958116292953</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.7199999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.2120146006345749</v>
+        <v>0.2120145857334137</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.2785477936267853</v>
+        <v>0.2785478234291077</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.5205200910568237</v>
+        <v>0.5205201506614685</v>
       </c>
       <c r="JB63" t="n">
         <v>0.4399999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.3396894633769989</v>
+        <v>0.3396895229816437</v>
       </c>
       <c r="JB64" t="n">
         <v>0.4399999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.7532278299331665</v>
+        <v>0.7532278895378113</v>
       </c>
       <c r="JB65" t="n">
         <v>0.4399999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.201208159327507</v>
+        <v>0.2012081742286682</v>
       </c>
       <c r="JB66" t="n">
         <v>0.16</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.1416998356580734</v>
+        <v>0.1416998207569122</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.4399999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.368494838476181</v>
+        <v>0.3684948980808258</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.7199999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.2603820860385895</v>
+        <v>0.2603821158409119</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.4399999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.2430460453033447</v>
+        <v>0.2430460155010223</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.4399999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.2621249854564667</v>
+        <v>0.2621249556541443</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.09278812259435654</v>
+        <v>0.09278809279203415</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.7199999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.3819985091686249</v>
+        <v>0.3819984495639801</v>
       </c>
       <c r="JB84" t="n">
         <v>0.4399999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.3484295606613159</v>
+        <v>0.3484295308589935</v>
       </c>
       <c r="JB86" t="n">
         <v>0.4399999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.3217560350894928</v>
+        <v>0.3217560648918152</v>
       </c>
       <c r="JB87" t="n">
         <v>0.3</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.699972927570343</v>
+        <v>0.6999729871749878</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.02000000000000007</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.5464195013046265</v>
+        <v>0.5464195609092712</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.4399999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.07968466728925705</v>
+        <v>0.07968470454216003</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.7199999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.3909324705600739</v>
+        <v>0.3909324407577515</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.4399999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.2790385484695435</v>
+        <v>0.2790385186672211</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.1600000000000001</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.4618848264217377</v>
+        <v>0.4618847668170929</v>
       </c>
       <c r="JB101" t="n">
         <v>0.3</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.2542849481105804</v>
+        <v>0.2542849183082581</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.7199999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.6019470691680908</v>
+        <v>0.601947009563446</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.8599999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.105463020503521</v>
+        <v>0.1054629907011986</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.8599999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.4863494038581848</v>
+        <v>0.4863494634628296</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.7199999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.2166753262281418</v>
+        <v>0.2166753709316254</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.7199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.1826610416173935</v>
+        <v>0.1826610565185547</v>
       </c>
       <c r="JB117" t="n">
         <v>0.16</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.302655816078186</v>
+        <v>0.3026559054851532</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.1199999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.2234208583831787</v>
+        <v>0.2234209179878235</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.7199999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.09578701108694077</v>
+        <v>0.09578698128461838</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.5799999999999998</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.3784999549388885</v>
+        <v>0.3784998655319214</v>
       </c>
       <c r="JB122" t="n">
         <v>0.3</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.1967712342739105</v>
+        <v>0.1967712193727493</v>
       </c>
       <c r="JB124" t="n">
         <v>0.3</v>
